--- a/2026 1-16 March Number.xlsx
+++ b/2026 1-16 March Number.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4454D43-A950-43A2-A929-BBD115D2DF90}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4364B755-EA7F-4106-B9B6-BC5639E6A126}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
@@ -111,6 +111,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -430,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D384"/>
+  <dimension ref="A1:D404"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -5815,6 +5819,286 @@
         <v>38.015998840332031</v>
       </c>
     </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A385" s="1">
+        <v>46097.958333333336</v>
+      </c>
+      <c r="B385" s="4">
+        <v>31.105882308062384</v>
+      </c>
+      <c r="C385" s="4">
+        <v>37.384765863418579</v>
+      </c>
+      <c r="D385" s="4">
+        <v>37.995600128173827</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A386" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B386" s="4">
+        <v>31.052631679334137</v>
+      </c>
+      <c r="C386" s="4">
+        <v>37.313541730244957</v>
+      </c>
+      <c r="D386" s="4">
+        <v>37.930799102783205</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A387" s="1">
+        <v>46098.041666666664</v>
+      </c>
+      <c r="B387" s="4">
+        <v>31.010416587193806</v>
+      </c>
+      <c r="C387" s="4">
+        <v>37.25416666666667</v>
+      </c>
+      <c r="D387" s="4">
+        <v>37.888800048828124</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A388" s="1">
+        <v>46098.083333333336</v>
+      </c>
+      <c r="B388" s="4">
+        <v>30.993749976158142</v>
+      </c>
+      <c r="C388" s="4">
+        <v>37.217788696289063</v>
+      </c>
+      <c r="D388" s="4">
+        <v>37.842999776204429</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A389" s="1">
+        <v>46098.125</v>
+      </c>
+      <c r="B389" s="4">
+        <v>30.951723953773236</v>
+      </c>
+      <c r="C389" s="4">
+        <v>37.176441779503456</v>
+      </c>
+      <c r="D389" s="4">
+        <v>37.7760009765625</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A390" s="1">
+        <v>46098.166666666664</v>
+      </c>
+      <c r="B390" s="4">
+        <v>30.918749862247044</v>
+      </c>
+      <c r="C390" s="4">
+        <v>37.133928298950195</v>
+      </c>
+      <c r="D390" s="4">
+        <v>37.751998901367188</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A391" s="1">
+        <v>46098.208333333336</v>
+      </c>
+      <c r="B391" s="4">
+        <v>30.994444246645326</v>
+      </c>
+      <c r="C391" s="4">
+        <v>37.174999745686847</v>
+      </c>
+      <c r="D391" s="4">
+        <v>37.697999954223633</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A392" s="1">
+        <v>46098.25</v>
+      </c>
+      <c r="B392" s="4">
+        <v>30.915909073569559</v>
+      </c>
+      <c r="C392" s="4">
+        <v>37.096428734915598</v>
+      </c>
+      <c r="D392" s="4">
+        <v>37.685999870300293</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A393" s="1">
+        <v>46098.291666666664</v>
+      </c>
+      <c r="B393" s="4">
+        <v>30.909615443303036</v>
+      </c>
+      <c r="C393" s="4">
+        <v>37.070833418104385</v>
+      </c>
+      <c r="D393" s="4">
+        <v>37.686000061035159</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A394" s="1">
+        <v>46098.333333333336</v>
+      </c>
+      <c r="B394" s="4">
+        <v>30.886110305786133</v>
+      </c>
+      <c r="C394" s="4">
+        <v>37.063194274902344</v>
+      </c>
+      <c r="D394" s="4">
+        <v>37.686000823974609</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A395" s="1">
+        <v>46098.375</v>
+      </c>
+      <c r="B395" s="4">
+        <v>30.857352425070371</v>
+      </c>
+      <c r="C395" s="4">
+        <v>37.025624847412111</v>
+      </c>
+      <c r="D395" s="4">
+        <v>37.691000620524086</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A396" s="1">
+        <v>46098.416666666664</v>
+      </c>
+      <c r="B396" s="4">
+        <v>30.882142748151505</v>
+      </c>
+      <c r="C396" s="4">
+        <v>37.072916666666664</v>
+      </c>
+      <c r="D396" s="4">
+        <v>37.746000289916992</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A397" s="1">
+        <v>46098.458333333336</v>
+      </c>
+      <c r="B397" s="4">
+        <v>30.921875</v>
+      </c>
+      <c r="C397" s="4">
+        <v>37.131771087646484</v>
+      </c>
+      <c r="D397" s="4">
+        <v>37.788000106811523</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A398" s="1">
+        <v>46098.5</v>
+      </c>
+      <c r="B398" s="4">
+        <v>30.920833428700764</v>
+      </c>
+      <c r="C398" s="4">
+        <v>37.145833333333336</v>
+      </c>
+      <c r="D398" s="4">
+        <v>37.739999771118164</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A399" s="1">
+        <v>46098.541666666664</v>
+      </c>
+      <c r="B399" s="4">
+        <v>30.950000127156574</v>
+      </c>
+      <c r="C399" s="4">
+        <v>37.18465874411843</v>
+      </c>
+      <c r="D399" s="4">
+        <v>37.819999694824219</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A400" s="1">
+        <v>46098.583333333336</v>
+      </c>
+      <c r="B400" s="4">
+        <v>30.931818181818183</v>
+      </c>
+      <c r="C400" s="4">
+        <v>37.203125</v>
+      </c>
+      <c r="D400" s="4">
+        <v>37.873999277750649</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A401" s="1">
+        <v>46098.625</v>
+      </c>
+      <c r="B401" s="4">
+        <v>31.016666730244953</v>
+      </c>
+      <c r="C401" s="4">
+        <v>37.289999898274736</v>
+      </c>
+      <c r="D401" s="4">
+        <v>37.949999237060545</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A402" s="1">
+        <v>46098.666666666664</v>
+      </c>
+      <c r="B402" s="4">
+        <v>31.071875333786011</v>
+      </c>
+      <c r="C402" s="4">
+        <v>37.339062690734863</v>
+      </c>
+      <c r="D402" s="4">
+        <v>37.986000061035156</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A403" s="1">
+        <v>46098.708333333336</v>
+      </c>
+      <c r="B403" s="4">
+        <v>31.045588100657742</v>
+      </c>
+      <c r="C403" s="4">
+        <v>37.354687213897705</v>
+      </c>
+      <c r="D403" s="4">
+        <v>38.002000172932945</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A404" s="1">
+        <v>46098.75</v>
+      </c>
+      <c r="B404" s="4">
+        <v>31</v>
+      </c>
+      <c r="C404" s="4">
+        <v>37.375</v>
+      </c>
+      <c r="D404" s="4">
+        <v>38.058000564575195</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026 1-16 March Number.xlsx
+++ b/2026 1-16 March Number.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4364B755-EA7F-4106-B9B6-BC5639E6A126}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{484AF363-8500-4415-A723-D550B19F390E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D404"/>
+  <dimension ref="A1:D419"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -6099,6 +6099,216 @@
         <v>38.058000564575195</v>
       </c>
     </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A405" s="1">
+        <v>46098.791666666664</v>
+      </c>
+      <c r="B405" s="4">
+        <v>31.046250057220458</v>
+      </c>
+      <c r="C405" s="4">
+        <v>37.38541634877523</v>
+      </c>
+      <c r="D405" s="4">
+        <v>38.047200012207028</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A406" s="1">
+        <v>46098.833333333336</v>
+      </c>
+      <c r="B406" s="4">
+        <v>31.0270836353302</v>
+      </c>
+      <c r="C406" s="4">
+        <v>37.379412033978632</v>
+      </c>
+      <c r="D406" s="4">
+        <v>38.027999877929688</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A407" s="1">
+        <v>46098.875</v>
+      </c>
+      <c r="B407" s="4">
+        <v>30.960714203970774</v>
+      </c>
+      <c r="C407" s="4">
+        <v>37.297794117647058</v>
+      </c>
+      <c r="D407" s="4">
+        <v>37.966799926757815</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A408" s="1">
+        <v>46098.916666666664</v>
+      </c>
+      <c r="B408" s="4">
+        <v>30.923077069796047</v>
+      </c>
+      <c r="C408" s="4">
+        <v>37.262500445048012</v>
+      </c>
+      <c r="D408" s="4">
+        <v>37.930499076843262</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A409" s="1">
+        <v>46098.958333333336</v>
+      </c>
+      <c r="B409" s="4">
+        <v>30.959782641866934</v>
+      </c>
+      <c r="C409" s="4">
+        <v>37.264204545454547</v>
+      </c>
+      <c r="D409" s="4">
+        <v>37.905999501546226</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A410" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B410" s="4">
+        <v>30.97361119588216</v>
+      </c>
+      <c r="C410" s="4">
+        <v>37.270312786102295</v>
+      </c>
+      <c r="D410" s="4">
+        <v>37.915500640869141</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A411" s="1">
+        <v>46099.041666666664</v>
+      </c>
+      <c r="B411" s="4">
+        <v>30.950000081743514</v>
+      </c>
+      <c r="C411" s="4">
+        <v>37.212500138716265</v>
+      </c>
+      <c r="D411" s="4">
+        <v>37.864799499511719</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A412" s="1">
+        <v>46099.083333333336</v>
+      </c>
+      <c r="B412" s="4">
+        <v>30.918181679465555</v>
+      </c>
+      <c r="C412" s="4">
+        <v>37.147395451863609</v>
+      </c>
+      <c r="D412" s="4">
+        <v>37.856000264485679</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A413" s="1">
+        <v>46099.125</v>
+      </c>
+      <c r="B413" s="4">
+        <v>30.899999976158142</v>
+      </c>
+      <c r="C413" s="4">
+        <v>37.098437309265137</v>
+      </c>
+      <c r="D413" s="4">
+        <v>37.855500221252441</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A414" s="1">
+        <v>46099.166666666664</v>
+      </c>
+      <c r="B414" s="4">
+        <v>30.891666412353516</v>
+      </c>
+      <c r="C414" s="4">
+        <v>37.077084011501739</v>
+      </c>
+      <c r="D414" s="4">
+        <v>37.820999145507813</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A415" s="1">
+        <v>46099.208333333336</v>
+      </c>
+      <c r="B415" s="4">
+        <v>30.899999737739563</v>
+      </c>
+      <c r="C415" s="4">
+        <v>37.07265567779541</v>
+      </c>
+      <c r="D415" s="4">
+        <v>37.760399627685544</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A416" s="1">
+        <v>46099.25</v>
+      </c>
+      <c r="B416" s="4">
+        <v>30.888235092163086</v>
+      </c>
+      <c r="C416" s="4">
+        <v>37.074519230769234</v>
+      </c>
+      <c r="D416" s="4">
+        <v>37.726800537109376</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A417" s="1">
+        <v>46099.291666666664</v>
+      </c>
+      <c r="B417" s="4">
+        <v>30.861666488647462</v>
+      </c>
+      <c r="C417" s="4">
+        <v>37.033333248562286</v>
+      </c>
+      <c r="D417" s="4">
+        <v>37.690999348958336</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A418" s="1">
+        <v>46099.333333333336</v>
+      </c>
+      <c r="B418" s="4">
+        <v>30.724999879535876</v>
+      </c>
+      <c r="C418" s="4">
+        <v>36.951562404632568</v>
+      </c>
+      <c r="D418" s="4">
+        <v>37.597200775146483</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A419" s="1">
+        <v>46099.375</v>
+      </c>
+      <c r="B419" s="4">
+        <v>30.588333129882813</v>
+      </c>
+      <c r="C419" s="4">
+        <v>36.804687817891441</v>
+      </c>
+      <c r="D419" s="4">
+        <v>37.459199523925783</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026 1-16 March Number.xlsx
+++ b/2026 1-16 March Number.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{484AF363-8500-4415-A723-D550B19F390E}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B6479CA-4639-4B11-841A-D48C196D8BC5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D419"/>
+  <dimension ref="A1:D433"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -6309,6 +6309,202 @@
         <v>37.459199523925783</v>
       </c>
     </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A420" s="1">
+        <v>46099.416666666664</v>
+      </c>
+      <c r="B420" s="4">
+        <v>30.667857578822545</v>
+      </c>
+      <c r="C420" s="4">
+        <v>36.891071864536833</v>
+      </c>
+      <c r="D420" s="4">
+        <v>37.509999593098961</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A421" s="1">
+        <v>46099.458333333336</v>
+      </c>
+      <c r="B421" s="4">
+        <v>30.796874523162842</v>
+      </c>
+      <c r="C421" s="4">
+        <v>37.011978785196938</v>
+      </c>
+      <c r="D421" s="4">
+        <v>37.697999954223633</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A422" s="1">
+        <v>46099.5</v>
+      </c>
+      <c r="B422" s="4">
+        <v>30.863234800450943</v>
+      </c>
+      <c r="C422" s="4">
+        <v>37.08035741533552</v>
+      </c>
+      <c r="D422" s="4">
+        <v>37.74799919128418</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A423" s="1">
+        <v>46099.541666666664</v>
+      </c>
+      <c r="B423" s="4">
+        <v>30.907142639160156</v>
+      </c>
+      <c r="C423" s="4">
+        <v>37.127083460489906</v>
+      </c>
+      <c r="D423" s="4">
+        <v>37.81350040435791</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A424" s="1">
+        <v>46099.583333333336</v>
+      </c>
+      <c r="B424" s="4">
+        <v>30.961904525756836</v>
+      </c>
+      <c r="C424" s="4">
+        <v>37.181249891008648</v>
+      </c>
+      <c r="D424" s="4">
+        <v>37.870000203450523</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A425" s="1">
+        <v>46099.625</v>
+      </c>
+      <c r="B425" s="4">
+        <v>31.00192304757925</v>
+      </c>
+      <c r="C425" s="4">
+        <v>37.238636363636367</v>
+      </c>
+      <c r="D425" s="4">
+        <v>37.900501251220703</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A426" s="1">
+        <v>46099.666666666664</v>
+      </c>
+      <c r="B426" s="4">
+        <v>31.0625</v>
+      </c>
+      <c r="C426" s="4">
+        <v>37.317857469831196</v>
+      </c>
+      <c r="D426" s="4">
+        <v>38.006000518798828</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A427" s="1">
+        <v>46099.708333333336</v>
+      </c>
+      <c r="B427" s="4">
+        <v>31.075000069358133</v>
+      </c>
+      <c r="C427" s="4">
+        <v>37.356250069358133</v>
+      </c>
+      <c r="D427" s="4">
+        <v>37.961999893188477</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A428" s="1">
+        <v>46099.75</v>
+      </c>
+      <c r="B428" s="4">
+        <v>31.10750045776367</v>
+      </c>
+      <c r="C428" s="4">
+        <v>37.442360772026909</v>
+      </c>
+      <c r="D428" s="4">
+        <v>38.027999877929688</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A429" s="1">
+        <v>46099.791666666664</v>
+      </c>
+      <c r="B429" s="4">
+        <v>31.086111386617024</v>
+      </c>
+      <c r="C429" s="4">
+        <v>37.437500238418579</v>
+      </c>
+      <c r="D429" s="4">
+        <v>38.052000045776367</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A430" s="1">
+        <v>46099.833333333336</v>
+      </c>
+      <c r="B430" s="4">
+        <v>31.047826020613961</v>
+      </c>
+      <c r="C430" s="4">
+        <v>37.418750286102295</v>
+      </c>
+      <c r="D430" s="4">
+        <v>38.082000732421875</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A431" s="1">
+        <v>46099.875</v>
+      </c>
+      <c r="B431" s="4">
+        <v>31.030434732851774</v>
+      </c>
+      <c r="C431" s="4">
+        <v>37.390277862548828</v>
+      </c>
+      <c r="D431" s="4">
+        <v>38.072001139322914</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A432" s="1">
+        <v>46099.916666666664</v>
+      </c>
+      <c r="B432" s="4">
+        <v>31.00694465637207</v>
+      </c>
+      <c r="C432" s="4">
+        <v>37.34635384877523</v>
+      </c>
+      <c r="D432" s="4">
+        <v>37.996500968933105</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A433" s="1">
+        <v>46099.958333333336</v>
+      </c>
+      <c r="B433" s="4">
+        <v>30.975000381469727</v>
+      </c>
+      <c r="C433" s="4">
+        <v>37.298751068115237</v>
+      </c>
+      <c r="D433" s="4">
+        <v>37.949999491373696</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026 1-16 March Number.xlsx
+++ b/2026 1-16 March Number.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B6479CA-4639-4B11-841A-D48C196D8BC5}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B55EB70-D8BB-4ED9-B5FB-4CA3194897F1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
@@ -111,10 +111,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -434,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D433"/>
+  <dimension ref="A1:D453"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -6496,14 +6492,286 @@
         <v>46099.958333333336</v>
       </c>
       <c r="B433" s="4">
-        <v>30.975000381469727</v>
+        <v>30.936111238267685</v>
       </c>
       <c r="C433" s="4">
-        <v>37.298751068115237</v>
+        <v>37.268269758958084</v>
       </c>
       <c r="D433" s="4">
-        <v>37.949999491373696</v>
-      </c>
+        <v>37.918799591064456</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A434" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B434" s="4">
+        <v>30.893749713897705</v>
+      </c>
+      <c r="C434" s="4">
+        <v>37.142187118530273</v>
+      </c>
+      <c r="D434" s="4">
+        <v>37.840000152587891</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A435" s="1">
+        <v>46100.041666666664</v>
+      </c>
+      <c r="B435" s="4">
+        <v>30.875</v>
+      </c>
+      <c r="C435" s="4">
+        <v>37.121875339084198</v>
+      </c>
+      <c r="D435" s="4">
+        <v>37.779000282287598</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A436" s="1">
+        <v>46100.083333333336</v>
+      </c>
+      <c r="B436" s="4">
+        <v>30.889999771118163</v>
+      </c>
+      <c r="C436" s="4">
+        <v>37.12812532697405</v>
+      </c>
+      <c r="D436" s="4">
+        <v>37.736000061035156</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A437" s="1">
+        <v>46100.125</v>
+      </c>
+      <c r="B437" s="4">
+        <v>30.894444359673393</v>
+      </c>
+      <c r="C437" s="4">
+        <v>37.115000915527347</v>
+      </c>
+      <c r="D437" s="4">
+        <v>37.694999694824219</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A438" s="1">
+        <v>46100.166666666664</v>
+      </c>
+      <c r="B438" s="4">
+        <v>30.9</v>
+      </c>
+      <c r="C438" s="4">
+        <v>37.116249465942381</v>
+      </c>
+      <c r="D438" s="4">
+        <v>37.681499481201172</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A439" s="1">
+        <v>46100.208333333336</v>
+      </c>
+      <c r="B439" s="4">
+        <v>30.881521142047383</v>
+      </c>
+      <c r="C439" s="4">
+        <v>37.114582697550453</v>
+      </c>
+      <c r="D439" s="4">
+        <v>37.608000437418617</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A440" s="1">
+        <v>46100.25</v>
+      </c>
+      <c r="B440" s="4">
+        <v>30.81874942779541</v>
+      </c>
+      <c r="C440" s="4">
+        <v>37.086607615152992</v>
+      </c>
+      <c r="D440" s="4">
+        <v>37.638000011444092</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A441" s="1">
+        <v>46100.291666666664</v>
+      </c>
+      <c r="B441" s="4">
+        <v>30.797726717862215</v>
+      </c>
+      <c r="C441" s="4">
+        <v>37.080859184265137</v>
+      </c>
+      <c r="D441" s="4">
+        <v>37.718571799142019</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A442" s="1">
+        <v>46100.333333333336</v>
+      </c>
+      <c r="B442" s="4">
+        <v>30.805999221801759</v>
+      </c>
+      <c r="C442" s="4">
+        <v>37.080434716266133</v>
+      </c>
+      <c r="D442" s="4">
+        <v>37.729000091552734</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A443" s="1">
+        <v>46100.375</v>
+      </c>
+      <c r="B443" s="4">
+        <v>30.848863168196246</v>
+      </c>
+      <c r="C443" s="4">
+        <v>37.112980769230766</v>
+      </c>
+      <c r="D443" s="4">
+        <v>37.74960021972656</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A444" s="1">
+        <v>46100.416666666664</v>
+      </c>
+      <c r="B444" s="4">
+        <v>30.863636363636363</v>
+      </c>
+      <c r="C444" s="4">
+        <v>37.115972306993271</v>
+      </c>
+      <c r="D444" s="4">
+        <v>37.702500343322754</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A445" s="1">
+        <v>46100.458333333336</v>
+      </c>
+      <c r="B445" s="4">
+        <v>30.88235305337345</v>
+      </c>
+      <c r="C445" s="4">
+        <v>37.128515243530273</v>
+      </c>
+      <c r="D445" s="4">
+        <v>37.799999999999997</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A446" s="1">
+        <v>46100.5</v>
+      </c>
+      <c r="B446" s="4">
+        <v>30.949999968210857</v>
+      </c>
+      <c r="C446" s="4">
+        <v>37.211666615804035</v>
+      </c>
+      <c r="D446" s="4">
+        <v>37.875</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A447" s="1">
+        <v>46100.541666666664</v>
+      </c>
+      <c r="B447" s="4">
+        <v>31.071666590372722</v>
+      </c>
+      <c r="C447" s="4">
+        <v>37.30833307902018</v>
+      </c>
+      <c r="D447" s="4">
+        <v>37.836000442504883</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A448" s="1">
+        <v>46100.583333333336</v>
+      </c>
+      <c r="B448" s="4">
+        <v>31.135000356038411</v>
+      </c>
+      <c r="C448" s="4">
+        <v>37.360795454545453</v>
+      </c>
+      <c r="D448" s="4">
+        <v>37.816500663757324</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A449" s="1">
+        <v>46100.625</v>
+      </c>
+      <c r="B449" s="4">
+        <v>31.177586851448847</v>
+      </c>
+      <c r="C449" s="4">
+        <v>37.404076451840609</v>
+      </c>
+      <c r="D449" s="4">
+        <v>37.822284698486328</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A450" s="1">
+        <v>46100.666666666664</v>
+      </c>
+      <c r="B450" s="4">
+        <v>31.270000171661376</v>
+      </c>
+      <c r="C450" s="4">
+        <v>37.488636016845703</v>
+      </c>
+      <c r="D450" s="4">
+        <v>37.906499862670898</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A451" s="1">
+        <v>46100.708333333336</v>
+      </c>
+      <c r="B451" s="4">
+        <v>31.316999969482421</v>
+      </c>
+      <c r="C451" s="4">
+        <v>37.54875005086263</v>
+      </c>
+      <c r="D451" s="4">
+        <v>37.952399444580081</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A452" s="1">
+        <v>46100.75</v>
+      </c>
+      <c r="B452" s="4">
+        <v>31.278571810041154</v>
+      </c>
+      <c r="C452" s="4">
+        <v>37.5390625</v>
+      </c>
+      <c r="D452" s="4">
+        <v>37.965000152587891</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A453" s="1"/>
+      <c r="B453" s="4"/>
+      <c r="C453" s="4"/>
+      <c r="D453" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026 1-16 March Number.xlsx
+++ b/2026 1-16 March Number.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B55EB70-D8BB-4ED9-B5FB-4CA3194897F1}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8050243-59F3-4BFA-8C4D-2B9F0B7A39EF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -111,6 +111,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -430,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D453"/>
+  <dimension ref="A1:D467"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -6758,20 +6762,224 @@
         <v>46100.75</v>
       </c>
       <c r="B452" s="4">
-        <v>31.278571810041154</v>
+        <v>31.260526355944183</v>
       </c>
       <c r="C452" s="4">
-        <v>37.5390625</v>
+        <v>37.516963958740234</v>
       </c>
       <c r="D452" s="4">
-        <v>37.965000152587891</v>
+        <v>37.944000244140625</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A453" s="1"/>
-      <c r="B453" s="4"/>
-      <c r="C453" s="4"/>
-      <c r="D453" s="4"/>
+      <c r="A453" s="1">
+        <v>46100.791666666664</v>
+      </c>
+      <c r="B453" s="4">
+        <v>31.227586614674536</v>
+      </c>
+      <c r="C453" s="4">
+        <v>37.511057340181793</v>
+      </c>
+      <c r="D453" s="4">
+        <v>37.954999923706055</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A454" s="1">
+        <v>46100.833333333336</v>
+      </c>
+      <c r="B454" s="4">
+        <v>31.210714476449148</v>
+      </c>
+      <c r="C454" s="4">
+        <v>37.485416412353516</v>
+      </c>
+      <c r="D454" s="4">
+        <v>38.035499572753906</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A455" s="1">
+        <v>46100.875</v>
+      </c>
+      <c r="B455" s="4">
+        <v>31.133333587646483</v>
+      </c>
+      <c r="C455" s="4">
+        <v>37.449062156677243</v>
+      </c>
+      <c r="D455" s="4">
+        <v>37.97760009765625</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A456" s="1">
+        <v>46100.916666666664</v>
+      </c>
+      <c r="B456" s="4">
+        <v>31.024999618530273</v>
+      </c>
+      <c r="C456" s="4">
+        <v>37.345454822887071</v>
+      </c>
+      <c r="D456" s="4">
+        <v>37.944000244140625</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A457" s="1">
+        <v>46100.958333333336</v>
+      </c>
+      <c r="B457" s="4">
+        <v>30.985000038146971</v>
+      </c>
+      <c r="C457" s="4">
+        <v>37.293749128069194</v>
+      </c>
+      <c r="D457" s="4">
+        <v>37.907999674479164</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A458" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B458" s="4">
+        <v>30.959374785423279</v>
+      </c>
+      <c r="C458" s="4">
+        <v>37.229166030883789</v>
+      </c>
+      <c r="D458" s="4">
+        <v>37.824857439313618</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A459" s="1">
+        <v>46101.041666666664</v>
+      </c>
+      <c r="B459" s="4">
+        <v>30.9375</v>
+      </c>
+      <c r="C459" s="4">
+        <v>37.197917090521919</v>
+      </c>
+      <c r="D459" s="4">
+        <v>37.791428702218191</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A460" s="1">
+        <v>46101.083333333336</v>
+      </c>
+      <c r="B460" s="4">
+        <v>30.907142639160156</v>
+      </c>
+      <c r="C460" s="4">
+        <v>37.122767857142854</v>
+      </c>
+      <c r="D460" s="4">
+        <v>37.732199859619143</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A461" s="1">
+        <v>46101.125</v>
+      </c>
+      <c r="B461" s="4">
+        <v>30.898213931492396</v>
+      </c>
+      <c r="C461" s="4">
+        <v>37.092500305175783</v>
+      </c>
+      <c r="D461" s="4">
+        <v>37.698000335693358</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A462" s="1">
+        <v>46101.166666666664</v>
+      </c>
+      <c r="B462" s="4">
+        <v>30.903571265084402</v>
+      </c>
+      <c r="C462" s="4">
+        <v>37.092361450195313</v>
+      </c>
+      <c r="D462" s="4">
+        <v>37.68999926249186</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A463" s="1">
+        <v>46101.208333333336</v>
+      </c>
+      <c r="B463" s="4">
+        <v>30.899999618530273</v>
+      </c>
+      <c r="C463" s="4">
+        <v>37.107954892245203</v>
+      </c>
+      <c r="D463" s="4">
+        <v>37.708999633789063</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A464" s="1">
+        <v>46101.25</v>
+      </c>
+      <c r="B464" s="4">
+        <v>30.856249968210857</v>
+      </c>
+      <c r="C464" s="4">
+        <v>37.06770865122477</v>
+      </c>
+      <c r="D464" s="4">
+        <v>37.677600097656253</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A465" s="1">
+        <v>46101.291666666664</v>
+      </c>
+      <c r="B465" s="4">
+        <v>30.859374761581421</v>
+      </c>
+      <c r="C465" s="4">
+        <v>37.069791793823242</v>
+      </c>
+      <c r="D465" s="4">
+        <v>37.703998565673828</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A466" s="1">
+        <v>46101.333333333336</v>
+      </c>
+      <c r="B466" s="4">
+        <v>30.795833428700764</v>
+      </c>
+      <c r="C466" s="4">
+        <v>37.046153435340294</v>
+      </c>
+      <c r="D466" s="4">
+        <v>37.685999734061106</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A467" s="1">
+        <v>46101.375</v>
+      </c>
+      <c r="B467" s="4">
+        <v>30.740625143051147</v>
+      </c>
+      <c r="C467" s="4">
+        <v>37.012500000000003</v>
+      </c>
+      <c r="D467" s="4">
+        <v>37.636000315348305</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026 1-16 March Number.xlsx
+++ b/2026 1-16 March Number.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8050243-59F3-4BFA-8C4D-2B9F0B7A39EF}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A748511-FCB5-4234-8642-8F12AA509F0A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D467"/>
+  <dimension ref="A1:D472"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -6972,13 +6972,83 @@
         <v>46101.375</v>
       </c>
       <c r="B467" s="4">
-        <v>30.740625143051147</v>
+        <v>30.741666793823242</v>
       </c>
       <c r="C467" s="4">
-        <v>37.012500000000003</v>
+        <v>36.990865267240082</v>
       </c>
       <c r="D467" s="4">
-        <v>37.636000315348305</v>
+        <v>37.644999821980797</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A468" s="1">
+        <v>46101.416666666664</v>
+      </c>
+      <c r="B468" s="4">
+        <v>30.786841743870784</v>
+      </c>
+      <c r="C468" s="4">
+        <v>37.055682095614344</v>
+      </c>
+      <c r="D468" s="4">
+        <v>37.670999526977539</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A469" s="1">
+        <v>46101.458333333336</v>
+      </c>
+      <c r="B469" s="4">
+        <v>30.870833396911621</v>
+      </c>
+      <c r="C469" s="4">
+        <v>37.100567904385656</v>
+      </c>
+      <c r="D469" s="4">
+        <v>37.726799774169919</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A470" s="1">
+        <v>46101.5</v>
+      </c>
+      <c r="B470" s="4">
+        <v>30.907692395723782</v>
+      </c>
+      <c r="C470" s="4">
+        <v>37.136363983154297</v>
+      </c>
+      <c r="D470" s="4">
+        <v>37.777713775634766</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A471" s="1">
+        <v>46101.541666666664</v>
+      </c>
+      <c r="B471" s="4">
+        <v>30.978125015894573</v>
+      </c>
+      <c r="C471" s="4">
+        <v>37.239062690734862</v>
+      </c>
+      <c r="D471" s="4">
+        <v>37.866000039236887</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A472" s="1">
+        <v>46101.583333333336</v>
+      </c>
+      <c r="B472" s="4">
+        <v>31.122222476535374</v>
+      </c>
+      <c r="C472" s="4">
+        <v>37.365104039510094</v>
+      </c>
+      <c r="D472" s="4">
+        <v>37.949332767062714</v>
       </c>
     </row>
   </sheetData>

--- a/2026 1-16 March Number.xlsx
+++ b/2026 1-16 March Number.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A748511-FCB5-4234-8642-8F12AA509F0A}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{897693E4-7BB6-470E-9E07-AD75CD6F3471}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D472"/>
+  <dimension ref="A1:D490"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -7042,13 +7042,265 @@
         <v>46101.583333333336</v>
       </c>
       <c r="B472" s="4">
-        <v>31.122222476535374</v>
+        <v>31.122916968663535</v>
       </c>
       <c r="C472" s="4">
-        <v>37.365104039510094</v>
+        <v>37.362562402089438</v>
       </c>
       <c r="D472" s="4">
-        <v>37.949332767062714</v>
+        <v>37.943588865880606</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A473" s="1">
+        <v>46101.625</v>
+      </c>
+      <c r="B473" s="4">
+        <v>31.229791665077208</v>
+      </c>
+      <c r="C473" s="4">
+        <v>37.442643070220946</v>
+      </c>
+      <c r="D473" s="4">
+        <v>38.048696801899062</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A474" s="1">
+        <v>46101.666666666664</v>
+      </c>
+      <c r="B474" s="4">
+        <v>31.304973491816455</v>
+      </c>
+      <c r="C474" s="4">
+        <v>37.523131854074045</v>
+      </c>
+      <c r="D474" s="4">
+        <v>38.125887742330683</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A475" s="1">
+        <v>46101.708333333336</v>
+      </c>
+      <c r="B475" s="4">
+        <v>31.338380840462698</v>
+      </c>
+      <c r="C475" s="4">
+        <v>37.547824687070289</v>
+      </c>
+      <c r="D475" s="4">
+        <v>38.161097717591538</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A476" s="1">
+        <v>46101.75</v>
+      </c>
+      <c r="B476" s="4">
+        <v>31.302620660997015</v>
+      </c>
+      <c r="C476" s="4">
+        <v>37.533101336007725</v>
+      </c>
+      <c r="D476" s="4">
+        <v>38.155345356159685</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A477" s="1">
+        <v>46101.791666666664</v>
+      </c>
+      <c r="B477" s="4">
+        <v>31.222359323931169</v>
+      </c>
+      <c r="C477" s="4">
+        <v>37.460602346173047</v>
+      </c>
+      <c r="D477" s="4">
+        <v>38.071991225244226</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A478" s="1">
+        <v>46101.833333333336</v>
+      </c>
+      <c r="B478" s="4">
+        <v>31.141484139362969</v>
+      </c>
+      <c r="C478" s="4">
+        <v>37.413038954734802</v>
+      </c>
+      <c r="D478" s="4">
+        <v>38.037361672120625</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A479" s="1">
+        <v>46101.875</v>
+      </c>
+      <c r="B479" s="4">
+        <v>31.104140720764796</v>
+      </c>
+      <c r="C479" s="4">
+        <v>37.369968452453612</v>
+      </c>
+      <c r="D479" s="4">
+        <v>37.996685391002231</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A480" s="1">
+        <v>46101.916666666664</v>
+      </c>
+      <c r="B480" s="4">
+        <v>31.073611185285781</v>
+      </c>
+      <c r="C480" s="4">
+        <v>37.348770464383641</v>
+      </c>
+      <c r="D480" s="4">
+        <v>37.98099462338827</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A481" s="1">
+        <v>46101.958333333336</v>
+      </c>
+      <c r="B481" s="4">
+        <v>31.03361086315579</v>
+      </c>
+      <c r="C481" s="4">
+        <v>37.316817839384633</v>
+      </c>
+      <c r="D481" s="4">
+        <v>37.943469072540516</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A482" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B482" s="4">
+        <v>31.063611268997192</v>
+      </c>
+      <c r="C482" s="4">
+        <v>37.313683410124341</v>
+      </c>
+      <c r="D482" s="4">
+        <v>37.904418340688132</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A483" s="1">
+        <v>46102.041666666664</v>
+      </c>
+      <c r="B483" s="4">
+        <v>31.004374965031943</v>
+      </c>
+      <c r="C483" s="4">
+        <v>37.273858480453491</v>
+      </c>
+      <c r="D483" s="4">
+        <v>37.884204936880231</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A484" s="1">
+        <v>46102.083333333336</v>
+      </c>
+      <c r="B484" s="4">
+        <v>30.957291682561237</v>
+      </c>
+      <c r="C484" s="4">
+        <v>37.197423273722329</v>
+      </c>
+      <c r="D484" s="4">
+        <v>37.838285728525314</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A485" s="1">
+        <v>46102.125</v>
+      </c>
+      <c r="B485" s="4">
+        <v>30.922291437784832</v>
+      </c>
+      <c r="C485" s="4">
+        <v>37.136451921295695</v>
+      </c>
+      <c r="D485" s="4">
+        <v>37.81042011397939</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A486" s="1">
+        <v>46102.166666666664</v>
+      </c>
+      <c r="B486" s="4">
+        <v>30.930139101876154</v>
+      </c>
+      <c r="C486" s="4">
+        <v>37.144749538800873</v>
+      </c>
+      <c r="D486" s="4">
+        <v>37.783119160762546</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A487" s="1">
+        <v>46102.208333333336</v>
+      </c>
+      <c r="B487" s="4">
+        <v>30.889652660157946</v>
+      </c>
+      <c r="C487" s="4">
+        <v>37.13064220216539</v>
+      </c>
+      <c r="D487" s="4">
+        <v>37.752767105389673</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A488" s="1">
+        <v>46102.25</v>
+      </c>
+      <c r="B488" s="4">
+        <v>30.844792079925536</v>
+      </c>
+      <c r="C488" s="4">
+        <v>37.097292327880858</v>
+      </c>
+      <c r="D488" s="4">
+        <v>37.750324588668299</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A489" s="1">
+        <v>46102.291666666664</v>
+      </c>
+      <c r="B489" s="4">
+        <v>30.847523154152764</v>
+      </c>
+      <c r="C489" s="4">
+        <v>37.105364640553795</v>
+      </c>
+      <c r="D489" s="4">
+        <v>37.758464131962043</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A490" s="1">
+        <v>46102.333333333336</v>
+      </c>
+      <c r="B490" s="4">
+        <v>30.830809683269926</v>
+      </c>
+      <c r="C490" s="4">
+        <v>37.119062423706055</v>
+      </c>
+      <c r="D490" s="4">
+        <v>37.781680042814813</v>
       </c>
     </row>
   </sheetData>
